--- a/Leitor_de_Fatura/Faturas_Analaiser/RIBEIRAO_Analaiser.xlsx
+++ b/Leitor_de_Fatura/Faturas_Analaiser/RIBEIRAO_Analaiser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\Leitor_de_Fatura\Faturas_Analaiser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD684B36-2DFD-40C1-BDE5-7965F165FED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA9E218-5DF5-40F0-9B82-2635C57FE098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1671,7 +1671,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>42</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>44</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>48</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>53</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>57</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>67</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>69</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>72</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>76</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>89</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>101</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>134</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>136</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>138</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>168</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>241</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>262</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>264</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>266</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>268</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>270</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>275</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>281</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>284</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>287</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>290</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>293</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>295</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>298</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>303</v>
       </c>
@@ -6941,10 +6941,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N127" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="3">
       <filters>
-        <filter val="A"/>
-        <filter val="IP"/>
+        <filter val="B4A"/>
       </filters>
     </filterColumn>
   </autoFilter>
